--- a/output_tunning/tabel_tuning_tcn.xlsx
+++ b/output_tunning/tabel_tuning_tcn.xlsx
@@ -491,10 +491,10 @@
         <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -502,13 +502,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1.1017</v>
+        <v>1.1718</v>
       </c>
       <c r="I2" t="n">
-        <v>8.31</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="3">
@@ -524,24 +524,24 @@
         <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1.1426</v>
+        <v>1.1109</v>
       </c>
       <c r="I3" t="n">
-        <v>14.45</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="4">
@@ -557,10 +557,10 @@
         <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -568,13 +568,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1.1487</v>
+        <v>1.1059</v>
       </c>
       <c r="I4" t="n">
-        <v>8.210000000000001</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="5">
@@ -590,24 +590,24 @@
         <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1.157</v>
+        <v>1.098</v>
       </c>
       <c r="I5" t="n">
-        <v>10.17</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="6">
@@ -623,10 +623,10 @@
         <v>32</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -634,13 +634,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1.1156</v>
+        <v>1.0987</v>
       </c>
       <c r="I6" t="n">
-        <v>7.45</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="7">
@@ -656,24 +656,24 @@
         <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2.8572</v>
+        <v>1.1485</v>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="8">
@@ -689,10 +689,10 @@
         <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -700,13 +700,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1.229</v>
+        <v>1.1325</v>
       </c>
       <c r="I8" t="n">
-        <v>6.19</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="9">
@@ -722,24 +722,24 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>2.2933</v>
+        <v>1.1467</v>
       </c>
       <c r="I9" t="n">
-        <v>6.1</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="10">
@@ -755,10 +755,10 @@
         <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.1946</v>
+        <v>1.1299</v>
       </c>
       <c r="I10" t="n">
-        <v>6.46</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="11">
@@ -788,24 +788,24 @@
         <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1.1368</v>
+        <v>1.1682</v>
       </c>
       <c r="I11" t="n">
-        <v>18.66</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="12">
@@ -821,10 +821,10 @@
         <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1.1427</v>
+        <v>1.0822</v>
       </c>
       <c r="I12" t="n">
-        <v>5.45</v>
+        <v>8.470000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -854,24 +854,24 @@
         <v>32</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.1474</v>
+        <v>1.0803</v>
       </c>
       <c r="I13" t="n">
-        <v>11.27</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="14">
@@ -887,10 +887,10 @@
         <v>32</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -898,13 +898,13 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.3501</v>
+        <v>1.2192</v>
       </c>
       <c r="I14" t="n">
-        <v>6.58</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="15">
@@ -920,24 +920,24 @@
         <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1.2553</v>
+        <v>1.1515</v>
       </c>
       <c r="I15" t="n">
-        <v>9.57</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="16">
@@ -953,10 +953,10 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1.1192</v>
+        <v>1.1087</v>
       </c>
       <c r="I16" t="n">
-        <v>10.53</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="17">
@@ -986,24 +986,24 @@
         <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1.2696</v>
+        <v>1.1546</v>
       </c>
       <c r="I17" t="n">
-        <v>17.6</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="18">
@@ -1019,10 +1019,10 @@
         <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1.0898</v>
+        <v>1.0776</v>
       </c>
       <c r="I18" t="n">
-        <v>10.04</v>
+        <v>12.94</v>
       </c>
     </row>
     <row r="19">
@@ -1052,24 +1052,24 @@
         <v>64</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.104</v>
+        <v>1.0684</v>
       </c>
       <c r="I19" t="n">
-        <v>18.53</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="20">
@@ -1085,10 +1085,10 @@
         <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1096,13 +1096,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1.0938</v>
+        <v>1.1115</v>
       </c>
       <c r="I20" t="n">
-        <v>10.13</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="21">
@@ -1118,24 +1118,24 @@
         <v>64</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1.0699</v>
+        <v>1.058</v>
       </c>
       <c r="I21" t="n">
-        <v>21.39</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="22">
@@ -1151,10 +1151,10 @@
         <v>64</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>1.1639</v>
+        <v>1.1159</v>
       </c>
       <c r="I22" t="n">
-        <v>7.73</v>
+        <v>9.640000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1184,24 +1184,24 @@
         <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>1.178</v>
+        <v>1.0672</v>
       </c>
       <c r="I23" t="n">
-        <v>18.08</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1217,10 +1217,10 @@
         <v>64</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1228,13 +1228,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>1.0966</v>
+        <v>1.094</v>
       </c>
       <c r="I24" t="n">
-        <v>8.51</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="25">
@@ -1250,24 +1250,24 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>1.3944</v>
+        <v>1.1099</v>
       </c>
       <c r="I25" t="n">
-        <v>6.97</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="26">
@@ -1283,10 +1283,10 @@
         <v>64</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>1.0958</v>
+        <v>1.0703</v>
       </c>
       <c r="I26" t="n">
-        <v>11.26</v>
+        <v>17.23</v>
       </c>
     </row>
     <row r="27">
@@ -1316,24 +1316,24 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1.1064</v>
+        <v>1.079</v>
       </c>
       <c r="I27" t="n">
-        <v>21.58</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="28">
@@ -1349,10 +1349,10 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1360,13 +1360,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>1.0801</v>
+        <v>1.1092</v>
       </c>
       <c r="I28" t="n">
-        <v>16.46</v>
+        <v>8.380000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1382,24 +1382,24 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>1.1585</v>
+        <v>1.0738</v>
       </c>
       <c r="I29" t="n">
-        <v>19.12</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="30">
@@ -1415,10 +1415,10 @@
         <v>64</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1426,13 +1426,13 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>1.1865</v>
+        <v>1.0781</v>
       </c>
       <c r="I30" t="n">
-        <v>11.79</v>
+        <v>18.01</v>
       </c>
     </row>
     <row r="31">
@@ -1448,24 +1448,24 @@
         <v>64</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>1.1542</v>
+        <v>1.0604</v>
       </c>
       <c r="I31" t="n">
-        <v>19.13</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="32">
@@ -1481,10 +1481,10 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1.2336</v>
+        <v>1.1202</v>
       </c>
       <c r="I32" t="n">
-        <v>10.65</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="33">
@@ -1514,24 +1514,24 @@
         <v>64</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>1.1533</v>
+        <v>1.1048</v>
       </c>
       <c r="I33" t="n">
-        <v>19.14</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1547,10 +1547,10 @@
         <v>32</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1558,13 +1558,13 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>1.2255</v>
+        <v>1.2453</v>
       </c>
       <c r="I34" t="n">
-        <v>11.97</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="35">
@@ -1580,24 +1580,24 @@
         <v>32</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>1.711</v>
+        <v>1.2187</v>
       </c>
       <c r="I35" t="n">
-        <v>8.880000000000001</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="36">
@@ -1613,10 +1613,10 @@
         <v>32</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>1.2131</v>
+        <v>1.203</v>
       </c>
       <c r="I36" t="n">
-        <v>12.74</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1646,24 +1646,24 @@
         <v>32</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>1.6306</v>
+        <v>1.1935</v>
       </c>
       <c r="I37" t="n">
-        <v>8.35</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="38">
@@ -1679,10 +1679,10 @@
         <v>32</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>1.2358</v>
+        <v>1.1807</v>
       </c>
       <c r="I38" t="n">
-        <v>7.94</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="39">
@@ -1712,24 +1712,24 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>1.6093</v>
+        <v>1.3156</v>
       </c>
       <c r="I39" t="n">
-        <v>6.02</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="40">
@@ -1745,10 +1745,10 @@
         <v>32</v>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1756,13 +1756,13 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>1.3749</v>
+        <v>1.2066</v>
       </c>
       <c r="I40" t="n">
-        <v>7.89</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="41">
@@ -1778,24 +1778,24 @@
         <v>32</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>1.9354</v>
+        <v>1.3198</v>
       </c>
       <c r="I41" t="n">
-        <v>7.1</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -1811,10 +1811,10 @@
         <v>32</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1822,13 +1822,13 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>1.3365</v>
+        <v>1.1878</v>
       </c>
       <c r="I42" t="n">
-        <v>10</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="43">
@@ -1844,24 +1844,24 @@
         <v>32</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>1.211</v>
+        <v>1.216</v>
       </c>
       <c r="I43" t="n">
-        <v>27.56</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="44">
@@ -1877,10 +1877,10 @@
         <v>32</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1888,13 +1888,13 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>1.2382</v>
+        <v>1.2163</v>
       </c>
       <c r="I44" t="n">
-        <v>9.460000000000001</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="45">
@@ -1910,24 +1910,24 @@
         <v>32</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>1.3697</v>
+        <v>1.3263</v>
       </c>
       <c r="I45" t="n">
-        <v>14.38</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="46">
@@ -1943,10 +1943,10 @@
         <v>32</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1954,13 +1954,13 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>1.3659</v>
+        <v>1.215</v>
       </c>
       <c r="I46" t="n">
-        <v>8.24</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -1976,24 +1976,24 @@
         <v>32</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>1.4623</v>
+        <v>1.3459</v>
       </c>
       <c r="I47" t="n">
-        <v>17.93</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="48">
@@ -2009,10 +2009,10 @@
         <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1.2631</v>
+        <v>1.2639</v>
       </c>
       <c r="I48" t="n">
         <v>9.789999999999999</v>
@@ -2042,24 +2042,24 @@
         <v>32</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>1.6692</v>
+        <v>1.2932</v>
       </c>
       <c r="I49" t="n">
-        <v>6.38</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="50">
@@ -2075,10 +2075,10 @@
         <v>64</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>1.2048</v>
+        <v>1.1971</v>
       </c>
       <c r="I50" t="n">
-        <v>16.5</v>
+        <v>13.11</v>
       </c>
     </row>
     <row r="51">
@@ -2108,24 +2108,24 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>1.229</v>
+        <v>1.2292</v>
       </c>
       <c r="I51" t="n">
-        <v>25.66</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="52">
@@ -2141,10 +2141,10 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>1.2361</v>
+        <v>1.1954</v>
       </c>
       <c r="I52" t="n">
-        <v>13.91</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="53">
@@ -2174,24 +2174,24 @@
         <v>64</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>1.4709</v>
+        <v>1.2209</v>
       </c>
       <c r="I53" t="n">
-        <v>10.6</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="54">
@@ -2207,10 +2207,10 @@
         <v>64</v>
       </c>
       <c r="D54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2218,13 +2218,13 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>1.2129</v>
+        <v>1.2451</v>
       </c>
       <c r="I54" t="n">
-        <v>11.85</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="55">
@@ -2240,24 +2240,24 @@
         <v>64</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>1.2982</v>
+        <v>1.2158</v>
       </c>
       <c r="I55" t="n">
-        <v>18.67</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="56">
@@ -2273,10 +2273,10 @@
         <v>64</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2284,13 +2284,13 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>1.3031</v>
+        <v>1.2206</v>
       </c>
       <c r="I56" t="n">
-        <v>12.58</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -2306,24 +2306,24 @@
         <v>64</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>1.5489</v>
+        <v>1.2239</v>
       </c>
       <c r="I57" t="n">
-        <v>6.69</v>
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -2339,10 +2339,10 @@
         <v>64</v>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2350,13 +2350,13 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>1.2431</v>
+        <v>1.302</v>
       </c>
       <c r="I58" t="n">
-        <v>14.62</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="59">
@@ -2372,24 +2372,24 @@
         <v>64</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>1.2946</v>
+        <v>1.3101</v>
       </c>
       <c r="I59" t="n">
-        <v>20.85</v>
+        <v>15.11</v>
       </c>
     </row>
     <row r="60">
@@ -2405,10 +2405,10 @@
         <v>64</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2416,13 +2416,13 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>1.3004</v>
+        <v>1.2667</v>
       </c>
       <c r="I60" t="n">
-        <v>14.2</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="61">
@@ -2438,24 +2438,24 @@
         <v>64</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>1.3014</v>
+        <v>1.181</v>
       </c>
       <c r="I61" t="n">
-        <v>16.38</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="62">
@@ -2471,10 +2471,10 @@
         <v>64</v>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2482,13 +2482,13 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>1.2861</v>
+        <v>1.1947</v>
       </c>
       <c r="I62" t="n">
-        <v>10.37</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="63">
@@ -2504,24 +2504,24 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E63" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>1.3088</v>
+        <v>1.2412</v>
       </c>
       <c r="I63" t="n">
-        <v>14.64</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="64">
@@ -2537,10 +2537,10 @@
         <v>64</v>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1.2708</v>
+        <v>1.2093</v>
       </c>
       <c r="I64" t="n">
-        <v>7.88</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
@@ -2570,24 +2570,24 @@
         <v>64</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>1.2952</v>
+        <v>1.1993</v>
       </c>
       <c r="I65" t="n">
-        <v>24.15</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="66">
@@ -2603,10 +2603,10 @@
         <v>32</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2614,13 +2614,13 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>1.3256</v>
+        <v>1.3908</v>
       </c>
       <c r="I66" t="n">
-        <v>7.75</v>
+        <v>8.08</v>
       </c>
     </row>
     <row r="67">
@@ -2636,24 +2636,24 @@
         <v>32</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>1.3951</v>
+        <v>1.409</v>
       </c>
       <c r="I67" t="n">
-        <v>15.41</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2669,10 +2669,10 @@
         <v>32</v>
       </c>
       <c r="D68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2680,13 +2680,13 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>1.3526</v>
+        <v>1.372</v>
       </c>
       <c r="I68" t="n">
-        <v>7.46</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="69">
@@ -2702,24 +2702,24 @@
         <v>32</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>1.4861</v>
+        <v>1.3623</v>
       </c>
       <c r="I69" t="n">
-        <v>16.11</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="70">
@@ -2735,10 +2735,10 @@
         <v>32</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>1.4502</v>
+        <v>1.3049</v>
       </c>
       <c r="I70" t="n">
-        <v>9.52</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="71">
@@ -2768,24 +2768,24 @@
         <v>32</v>
       </c>
       <c r="D71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>1.8825</v>
+        <v>1.4266</v>
       </c>
       <c r="I71" t="n">
-        <v>8.279999999999999</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="72">
@@ -2801,10 +2801,10 @@
         <v>32</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2812,13 +2812,13 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>1.6192</v>
+        <v>1.4155</v>
       </c>
       <c r="I72" t="n">
-        <v>5.4</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="73">
@@ -2834,24 +2834,24 @@
         <v>32</v>
       </c>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>2.3782</v>
+        <v>1.3468</v>
       </c>
       <c r="I73" t="n">
-        <v>5.99</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="74">
@@ -2867,10 +2867,10 @@
         <v>32</v>
       </c>
       <c r="D74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E74" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2878,13 +2878,13 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>1.3974</v>
+        <v>1.5255</v>
       </c>
       <c r="I74" t="n">
-        <v>8.58</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="75">
@@ -2900,24 +2900,24 @@
         <v>32</v>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E75" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>1.4011</v>
+        <v>1.3604</v>
       </c>
       <c r="I75" t="n">
-        <v>23.32</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="76">
@@ -2933,10 +2933,10 @@
         <v>32</v>
       </c>
       <c r="D76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2944,13 +2944,13 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>1.3229</v>
+        <v>1.3134</v>
       </c>
       <c r="I76" t="n">
-        <v>7.3</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="77">
@@ -2966,24 +2966,24 @@
         <v>32</v>
       </c>
       <c r="D77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>1.3724</v>
+        <v>1.3044</v>
       </c>
       <c r="I77" t="n">
-        <v>6.69</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -2999,10 +2999,10 @@
         <v>32</v>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3010,13 +3010,13 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>1.5021</v>
+        <v>1.505</v>
       </c>
       <c r="I78" t="n">
-        <v>7.49</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="79">
@@ -3032,24 +3032,24 @@
         <v>32</v>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>2.1877</v>
+        <v>1.3315</v>
       </c>
       <c r="I79" t="n">
-        <v>6.59</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="80">
@@ -3065,10 +3065,10 @@
         <v>32</v>
       </c>
       <c r="D80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E80" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3076,13 +3076,13 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>1.6018</v>
+        <v>1.4629</v>
       </c>
       <c r="I80" t="n">
-        <v>8.470000000000001</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="81">
@@ -3098,24 +3098,24 @@
         <v>32</v>
       </c>
       <c r="D81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E81" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>2.0128</v>
+        <v>1.3956</v>
       </c>
       <c r="I81" t="n">
-        <v>5.47</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3131,10 +3131,10 @@
         <v>64</v>
       </c>
       <c r="D82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3142,13 +3142,13 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>1.3781</v>
+        <v>1.4476</v>
       </c>
       <c r="I82" t="n">
-        <v>7.9</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="83">
@@ -3164,24 +3164,24 @@
         <v>64</v>
       </c>
       <c r="D83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>1.3817</v>
+        <v>1.3932</v>
       </c>
       <c r="I83" t="n">
-        <v>17.91</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="84">
@@ -3197,10 +3197,10 @@
         <v>64</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3208,13 +3208,13 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>1.3274</v>
+        <v>1.3419</v>
       </c>
       <c r="I84" t="n">
-        <v>10.42</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="85">
@@ -3230,24 +3230,24 @@
         <v>64</v>
       </c>
       <c r="D85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>1.4171</v>
+        <v>1.3372</v>
       </c>
       <c r="I85" t="n">
-        <v>14.04</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="86">
@@ -3263,10 +3263,10 @@
         <v>64</v>
       </c>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3274,13 +3274,13 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>1.3463</v>
+        <v>1.3925</v>
       </c>
       <c r="I86" t="n">
-        <v>14.31</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="87">
@@ -3296,24 +3296,24 @@
         <v>64</v>
       </c>
       <c r="D87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>1.6607</v>
+        <v>1.3861</v>
       </c>
       <c r="I87" t="n">
-        <v>9.449999999999999</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="88">
@@ -3329,10 +3329,10 @@
         <v>64</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3340,13 +3340,13 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>1.5289</v>
+        <v>1.3438</v>
       </c>
       <c r="I88" t="n">
-        <v>8.15</v>
+        <v>12.45</v>
       </c>
     </row>
     <row r="89">
@@ -3362,24 +3362,24 @@
         <v>64</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>1.6907</v>
+        <v>1.346</v>
       </c>
       <c r="I89" t="n">
-        <v>6.52</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="90">
@@ -3395,10 +3395,10 @@
         <v>64</v>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E90" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>1.3511</v>
+        <v>1.3757</v>
       </c>
       <c r="I90" t="n">
-        <v>16.38</v>
+        <v>12.85</v>
       </c>
     </row>
     <row r="91">
@@ -3428,24 +3428,24 @@
         <v>64</v>
       </c>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>1.3562</v>
+        <v>1.3355</v>
       </c>
       <c r="I91" t="n">
-        <v>25.34</v>
+        <v>12.93</v>
       </c>
     </row>
     <row r="92">
@@ -3461,10 +3461,10 @@
         <v>64</v>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3472,13 +3472,13 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>1.3697</v>
+        <v>1.3527</v>
       </c>
       <c r="I92" t="n">
-        <v>13.07</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="93">
@@ -3494,24 +3494,24 @@
         <v>64</v>
       </c>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E93" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>1.3986</v>
+        <v>1.3658</v>
       </c>
       <c r="I93" t="n">
-        <v>16.75</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="94">
@@ -3527,24 +3527,24 @@
         <v>64</v>
       </c>
       <c r="D94" t="n">
+        <v>3</v>
+      </c>
+      <c r="E94" t="n">
+        <v>8</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
         <v>5</v>
       </c>
-      <c r="E94" t="n">
-        <v>16</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>0.001</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
-        <v>7</v>
-      </c>
       <c r="H94" s="2" t="n">
-        <v>1.3874</v>
+        <v>1.416</v>
       </c>
       <c r="I94" t="n">
-        <v>10.02</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="95">
@@ -3560,24 +3560,24 @@
         <v>64</v>
       </c>
       <c r="D95" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E95" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>1.3976</v>
+        <v>1.4112</v>
       </c>
       <c r="I95" t="n">
-        <v>18.52</v>
+        <v>20.21</v>
       </c>
     </row>
     <row r="96">
@@ -3593,10 +3593,10 @@
         <v>64</v>
       </c>
       <c r="D96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E96" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3604,13 +3604,13 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>1.4028</v>
+        <v>1.3569</v>
       </c>
       <c r="I96" t="n">
-        <v>10.83</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="97">
@@ -3626,24 +3626,24 @@
         <v>64</v>
       </c>
       <c r="D97" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E97" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0.0001</t>
+          <t>0.0015</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>1.7849</v>
+        <v>1.3778</v>
       </c>
       <c r="I97" t="n">
-        <v>7.38</v>
+        <v>10.88</v>
       </c>
     </row>
   </sheetData>
